--- a/src/result/olivetti/model_comparison.xlsx
+++ b/src/result/olivetti/model_comparison.xlsx
@@ -483,16 +483,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.401060342788696</v>
+        <v>1.565907955169678</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01220488548278809</v>
+        <v>0.009999275207519531</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01520586013793945</v>
+        <v>0.0142064094543457</v>
       </c>
       <c r="E4" t="n">
-        <v>4.303313016891479</v>
+        <v>6.687695741653442</v>
       </c>
     </row>
   </sheetData>

--- a/src/result/olivetti/model_comparison.xlsx
+++ b/src/result/olivetti/model_comparison.xlsx
@@ -483,16 +483,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.565907955169678</v>
+        <v>2.909066200256348</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009999275207519531</v>
+        <v>0.01325321197509766</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0142064094543457</v>
+        <v>0.01415729522705078</v>
       </c>
       <c r="E4" t="n">
-        <v>6.687695741653442</v>
+        <v>7.030608654022217</v>
       </c>
     </row>
   </sheetData>

--- a/src/result/olivetti/model_comparison.xlsx
+++ b/src/result/olivetti/model_comparison.xlsx
@@ -413,86 +413,100 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E1" t="n">
-        <v>3</v>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>precision</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>f1_score</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
           <t>KNN</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>SVM Linear</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>SVM RBF</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>SVM Best</t>
-        </is>
+      <c r="B2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.9548333333333333</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.9393968253968253</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.003044366836547852</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>SVM Linear</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="C3" t="n">
+        <v>0.9570000000000001</v>
+      </c>
+      <c r="D3" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="D3" t="n">
-        <v>0.92</v>
-      </c>
       <c r="E3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9403412698412699</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.07090854644775391</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>SVM RBF</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.909066200256348</v>
+        <v>0.92</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01325321197509766</v>
+        <v>0.9458333333333333</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01415729522705078</v>
+        <v>0.92</v>
       </c>
       <c r="E4" t="n">
-        <v>7.030608654022217</v>
+        <v>0.9197777777777779</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.08388566970825195</v>
       </c>
     </row>
   </sheetData>

--- a/src/result/olivetti/model_comparison.xlsx
+++ b/src/result/olivetti/model_comparison.xlsx
@@ -413,100 +413,85 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>f1_score</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
+      <c r="A2" t="n">
+        <v>0.9399999999999999</v>
       </c>
       <c r="B2" t="n">
+        <v>0.9548333333333333</v>
+      </c>
+      <c r="C2" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="C2" t="n">
-        <v>0.9548333333333333</v>
-      </c>
       <c r="D2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9393968253968253</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9393968253968253</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.001997709274291992</v>
+        <v>0.003080844879150391</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>SVM Linear</t>
-        </is>
+      <c r="A3" t="n">
+        <v>0.9399999999999999</v>
       </c>
       <c r="B3" t="n">
+        <v>0.9570000000000001</v>
+      </c>
+      <c r="C3" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.9570000000000001</v>
-      </c>
       <c r="D3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9403412698412699</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9403412698412699</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.0683281421661377</v>
+        <v>0.01100802421569824</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>SVM RBF</t>
-        </is>
+      <c r="A4" t="n">
+        <v>0.92</v>
       </c>
       <c r="B4" t="n">
+        <v>0.9458333333333333</v>
+      </c>
+      <c r="C4" t="n">
         <v>0.92</v>
       </c>
-      <c r="C4" t="n">
-        <v>0.9458333333333333</v>
-      </c>
       <c r="D4" t="n">
-        <v>0.92</v>
+        <v>0.9197777777777779</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9197777777777779</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.07763123512268066</v>
+        <v>0.08504724502563477</v>
       </c>
     </row>
   </sheetData>
